--- a/vendor_list.xlsx
+++ b/vendor_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Digital_Life\06_Work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pallavi.pen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4CED96-6566-43D2-9A2B-0CD9E6D7D3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A364B01C-2407-4F18-980A-063D97E18459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F29C8DE6-4C93-4303-B28F-F3BD5FAA3955}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="864">
   <si>
     <t>Vendor Name</t>
   </si>
@@ -2614,13 +2614,25 @@
   </si>
   <si>
     <t>Primary banking institution; holds company accounts and processes financial transactions</t>
+  </si>
+  <si>
+    <t>Gafana Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://grafana.com</t>
+  </si>
+  <si>
+    <t>https://trust.grafana.com</t>
+  </si>
+  <si>
+    <t>Infra Monitoring tool.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2661,6 +2673,14 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2706,7 +2726,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2729,11 +2749,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2774,8 +2806,16 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3088,7 +3128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F015D71-419B-4249-B5EE-022B19095D79}">
-  <dimension ref="A1:F254"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr defaultColWidth="32.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
@@ -3191,7 +3231,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -3211,7 +3251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>26</v>
       </c>
@@ -3231,7 +3271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
@@ -3251,7 +3291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
@@ -3271,7 +3311,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -3291,7 +3331,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>40</v>
       </c>
@@ -3311,7 +3351,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -3331,7 +3371,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>46</v>
       </c>
@@ -3351,7 +3391,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3371,7 +3411,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
@@ -3391,7 +3431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -3411,7 +3451,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>60</v>
       </c>
@@ -3431,7 +3471,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
@@ -3451,7 +3491,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>68</v>
       </c>
@@ -3471,7 +3511,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>71</v>
       </c>
@@ -3491,7 +3531,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>74</v>
       </c>
@@ -3511,7 +3551,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>77</v>
       </c>
@@ -3531,7 +3571,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>80</v>
       </c>
@@ -3551,7 +3591,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>83</v>
       </c>
@@ -3571,7 +3611,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>86</v>
       </c>
@@ -3591,7 +3631,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>90</v>
       </c>
@@ -3611,7 +3651,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>93</v>
       </c>
@@ -3631,7 +3671,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>97</v>
       </c>
@@ -3651,7 +3691,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>100</v>
       </c>
@@ -3671,7 +3711,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>103</v>
       </c>
@@ -3691,7 +3731,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>108</v>
       </c>
@@ -3711,7 +3751,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>111</v>
       </c>
@@ -3731,7 +3771,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>115</v>
       </c>
@@ -3751,7 +3791,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>119</v>
       </c>
@@ -3771,7 +3811,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>122</v>
       </c>
@@ -3791,7 +3831,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>125</v>
       </c>
@@ -3811,7 +3851,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>129</v>
       </c>
@@ -3831,7 +3871,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>133</v>
       </c>
@@ -3851,7 +3891,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>136</v>
       </c>
@@ -3871,7 +3911,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>139</v>
       </c>
@@ -3891,7 +3931,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>143</v>
       </c>
@@ -3911,7 +3951,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>146</v>
       </c>
@@ -3931,7 +3971,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>150</v>
       </c>
@@ -3951,7 +3991,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>153</v>
       </c>
@@ -3971,7 +4011,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>155</v>
       </c>
@@ -3991,7 +4031,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>158</v>
       </c>
@@ -4011,7 +4051,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>161</v>
       </c>
@@ -4031,7 +4071,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>165</v>
       </c>
@@ -4051,7 +4091,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>168</v>
       </c>
@@ -4071,7 +4111,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>171</v>
       </c>
@@ -4091,7 +4131,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>173</v>
       </c>
@@ -4111,7 +4151,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>177</v>
       </c>
@@ -4131,7 +4171,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>182</v>
       </c>
@@ -4151,7 +4191,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>185</v>
       </c>
@@ -4171,7 +4211,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>189</v>
       </c>
@@ -4191,7 +4231,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>192</v>
       </c>
@@ -4211,7 +4251,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>196</v>
       </c>
@@ -4231,7 +4271,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>199</v>
       </c>
@@ -4251,7 +4291,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>203</v>
       </c>
@@ -4271,7 +4311,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>207</v>
       </c>
@@ -4291,7 +4331,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>210</v>
       </c>
@@ -4311,7 +4351,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>214</v>
       </c>
@@ -4331,7 +4371,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>217</v>
       </c>
@@ -4351,7 +4391,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>222</v>
       </c>
@@ -4371,7 +4411,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>226</v>
       </c>
@@ -4391,7 +4431,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>231</v>
       </c>
@@ -4411,7 +4451,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>235</v>
       </c>
@@ -4431,7 +4471,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>239</v>
       </c>
@@ -4451,7 +4491,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>243</v>
       </c>
@@ -4471,7 +4511,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>246</v>
       </c>
@@ -4491,7 +4531,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>250</v>
       </c>
@@ -4511,7 +4551,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>254</v>
       </c>
@@ -4531,7 +4571,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>257</v>
       </c>
@@ -4551,7 +4591,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>261</v>
       </c>
@@ -4571,7 +4611,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>265</v>
       </c>
@@ -4591,7 +4631,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>268</v>
       </c>
@@ -4611,7 +4651,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>269</v>
       </c>
@@ -4631,7 +4671,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>272</v>
       </c>
@@ -4651,7 +4691,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>275</v>
       </c>
@@ -4671,7 +4711,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>276</v>
       </c>
@@ -4691,7 +4731,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>279</v>
       </c>
@@ -4711,7 +4751,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>283</v>
       </c>
@@ -4731,7 +4771,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>286</v>
       </c>
@@ -4751,7 +4791,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>290</v>
       </c>
@@ -4771,7 +4811,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>294</v>
       </c>
@@ -4791,7 +4831,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>297</v>
       </c>
@@ -4811,7 +4851,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>299</v>
       </c>
@@ -4831,7 +4871,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>303</v>
       </c>
@@ -4851,7 +4891,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>307</v>
       </c>
@@ -4871,7 +4911,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>311</v>
       </c>
@@ -4891,7 +4931,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>314</v>
       </c>
@@ -4911,7 +4951,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>318</v>
       </c>
@@ -4931,7 +4971,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>321</v>
       </c>
@@ -4951,7 +4991,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>325</v>
       </c>
@@ -4971,7 +5011,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>329</v>
       </c>
@@ -4991,7 +5031,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>333</v>
       </c>
@@ -5011,7 +5051,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>336</v>
       </c>
@@ -5031,7 +5071,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>339</v>
       </c>
@@ -5051,7 +5091,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
         <v>343</v>
       </c>
@@ -5071,7 +5111,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>347</v>
       </c>
@@ -5091,7 +5131,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
         <v>351</v>
       </c>
@@ -5111,7 +5151,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>355</v>
       </c>
@@ -5131,7 +5171,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
         <v>359</v>
       </c>
@@ -5151,7 +5191,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>363</v>
       </c>
@@ -5171,7 +5211,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
         <v>366</v>
       </c>
@@ -5191,7 +5231,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>370</v>
       </c>
@@ -5211,7 +5251,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
         <v>374</v>
       </c>
@@ -5231,7 +5271,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>376</v>
       </c>
@@ -5251,7 +5291,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>380</v>
       </c>
@@ -5271,7 +5311,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>383</v>
       </c>
@@ -5291,7 +5331,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
         <v>386</v>
       </c>
@@ -5311,7 +5351,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>388</v>
       </c>
@@ -5331,7 +5371,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
         <v>392</v>
       </c>
@@ -5351,7 +5391,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>396</v>
       </c>
@@ -5371,7 +5411,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
         <v>400</v>
       </c>
@@ -5391,7 +5431,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>402</v>
       </c>
@@ -5411,7 +5451,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
         <v>405</v>
       </c>
@@ -5431,7 +5471,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>409</v>
       </c>
@@ -5451,7 +5491,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
         <v>413</v>
       </c>
@@ -5471,7 +5511,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>416</v>
       </c>
@@ -5491,7 +5531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
         <v>418</v>
       </c>
@@ -5511,7 +5551,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>421</v>
       </c>
@@ -5531,7 +5571,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
         <v>424</v>
       </c>
@@ -5551,7 +5591,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>427</v>
       </c>
@@ -5571,7 +5611,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
         <v>431</v>
       </c>
@@ -5591,7 +5631,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>434</v>
       </c>
@@ -5611,7 +5651,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
         <v>437</v>
       </c>
@@ -5631,7 +5671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>440</v>
       </c>
@@ -5651,7 +5691,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
         <v>443</v>
       </c>
@@ -5671,7 +5711,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>446</v>
       </c>
@@ -5691,7 +5731,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
         <v>450</v>
       </c>
@@ -5711,7 +5751,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>454</v>
       </c>
@@ -5731,7 +5771,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
         <v>457</v>
       </c>
@@ -5751,7 +5791,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>460</v>
       </c>
@@ -5771,7 +5811,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
         <v>463</v>
       </c>
@@ -5791,7 +5831,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>466</v>
       </c>
@@ -5811,7 +5851,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
         <v>470</v>
       </c>
@@ -5831,7 +5871,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>474</v>
       </c>
@@ -5851,7 +5891,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
         <v>477</v>
       </c>
@@ -5871,7 +5911,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>480</v>
       </c>
@@ -5891,7 +5931,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
         <v>483</v>
       </c>
@@ -5911,7 +5951,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>485</v>
       </c>
@@ -5931,7 +5971,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A143" s="7" t="s">
         <v>487</v>
       </c>
@@ -5951,7 +5991,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>490</v>
       </c>
@@ -5971,7 +6011,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="s">
         <v>492</v>
       </c>
@@ -5991,7 +6031,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>496</v>
       </c>
@@ -6011,7 +6051,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
         <v>500</v>
       </c>
@@ -6031,7 +6071,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>503</v>
       </c>
@@ -6051,7 +6091,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
         <v>507</v>
       </c>
@@ -6071,7 +6111,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>511</v>
       </c>
@@ -6091,7 +6131,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
         <v>515</v>
       </c>
@@ -6111,7 +6151,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>519</v>
       </c>
@@ -6131,7 +6171,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
         <v>522</v>
       </c>
@@ -6151,7 +6191,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>525</v>
       </c>
@@ -6171,7 +6211,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
         <v>529</v>
       </c>
@@ -6191,7 +6231,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>533</v>
       </c>
@@ -6211,7 +6251,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="s">
         <v>536</v>
       </c>
@@ -6231,7 +6271,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>540</v>
       </c>
@@ -6251,7 +6291,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
         <v>544</v>
       </c>
@@ -6271,7 +6311,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>547</v>
       </c>
@@ -6291,7 +6331,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
         <v>551</v>
       </c>
@@ -6311,7 +6351,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>554</v>
       </c>
@@ -6331,7 +6371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
         <v>557</v>
       </c>
@@ -6351,7 +6391,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>561</v>
       </c>
@@ -6371,7 +6411,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
         <v>565</v>
       </c>
@@ -6391,7 +6431,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>569</v>
       </c>
@@ -6411,7 +6451,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="s">
         <v>573</v>
       </c>
@@ -6431,7 +6471,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>577</v>
       </c>
@@ -6451,7 +6491,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="s">
         <v>580</v>
       </c>
@@ -6471,7 +6511,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>583</v>
       </c>
@@ -6491,7 +6531,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
         <v>587</v>
       </c>
@@ -6511,7 +6551,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>591</v>
       </c>
@@ -6531,7 +6571,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="s">
         <v>594</v>
       </c>
@@ -6551,7 +6591,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>597</v>
       </c>
@@ -6571,7 +6611,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="s">
         <v>601</v>
       </c>
@@ -6591,7 +6631,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>604</v>
       </c>
@@ -6611,7 +6651,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="s">
         <v>607</v>
       </c>
@@ -6631,7 +6671,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>610</v>
       </c>
@@ -6651,7 +6691,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="s">
         <v>614</v>
       </c>
@@ -6671,7 +6711,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>618</v>
       </c>
@@ -6691,7 +6731,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
         <v>620</v>
       </c>
@@ -6711,7 +6751,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>623</v>
       </c>
@@ -6731,7 +6771,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
         <v>626</v>
       </c>
@@ -6751,7 +6791,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>629</v>
       </c>
@@ -6771,7 +6811,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="s">
         <v>633</v>
       </c>
@@ -6791,7 +6831,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>635</v>
       </c>
@@ -6811,7 +6851,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
         <v>638</v>
       </c>
@@ -6831,7 +6871,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>641</v>
       </c>
@@ -6851,7 +6891,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
         <v>644</v>
       </c>
@@ -6871,7 +6911,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>648</v>
       </c>
@@ -6891,7 +6931,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
         <v>652</v>
       </c>
@@ -6911,7 +6951,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>655</v>
       </c>
@@ -6931,7 +6971,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
         <v>658</v>
       </c>
@@ -6951,7 +6991,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>661</v>
       </c>
@@ -6971,7 +7011,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="s">
         <v>664</v>
       </c>
@@ -6991,7 +7031,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>668</v>
       </c>
@@ -7011,7 +7051,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>671</v>
       </c>
@@ -7031,7 +7071,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>674</v>
       </c>
@@ -7051,7 +7091,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>677</v>
       </c>
@@ -7071,7 +7111,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>680</v>
       </c>
@@ -7091,7 +7131,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>683</v>
       </c>
@@ -7111,7 +7151,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>686</v>
       </c>
@@ -7131,7 +7171,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>689</v>
       </c>
@@ -7151,7 +7191,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>692</v>
       </c>
@@ -7171,7 +7211,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
         <v>694</v>
       </c>
@@ -7191,7 +7231,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>697</v>
       </c>
@@ -7211,7 +7251,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
         <v>701</v>
       </c>
@@ -7231,7 +7271,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>705</v>
       </c>
@@ -7251,7 +7291,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="s">
         <v>708</v>
       </c>
@@ -7269,7 +7309,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>709</v>
       </c>
@@ -7289,7 +7329,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A211" s="7" t="s">
         <v>712</v>
       </c>
@@ -7309,7 +7349,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>715</v>
       </c>
@@ -7329,7 +7369,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A213" s="7" t="s">
         <v>718</v>
       </c>
@@ -7349,7 +7389,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>720</v>
       </c>
@@ -7369,7 +7409,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
         <v>721</v>
       </c>
@@ -7389,7 +7429,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>724</v>
       </c>
@@ -7409,7 +7449,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A217" s="7" t="s">
         <v>727</v>
       </c>
@@ -7429,7 +7469,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>730</v>
       </c>
@@ -7449,7 +7489,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A219" s="7" t="s">
         <v>733</v>
       </c>
@@ -7469,7 +7509,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>736</v>
       </c>
@@ -7489,7 +7529,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A221" s="7" t="s">
         <v>739</v>
       </c>
@@ -7509,7 +7549,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>743</v>
       </c>
@@ -7529,7 +7569,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A223" s="7" t="s">
         <v>747</v>
       </c>
@@ -7549,7 +7589,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>750</v>
       </c>
@@ -7569,7 +7609,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A225" s="7" t="s">
         <v>754</v>
       </c>
@@ -7589,7 +7629,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>757</v>
       </c>
@@ -7609,7 +7649,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A227" s="7" t="s">
         <v>760</v>
       </c>
@@ -7629,7 +7669,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>764</v>
       </c>
@@ -7649,7 +7689,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>768</v>
       </c>
@@ -7669,7 +7709,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>771</v>
       </c>
@@ -7689,7 +7729,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>775</v>
       </c>
@@ -7709,7 +7749,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>778</v>
       </c>
@@ -7729,7 +7769,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>781</v>
       </c>
@@ -7749,7 +7789,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>785</v>
       </c>
@@ -7769,7 +7809,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>789</v>
       </c>
@@ -7789,7 +7829,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>793</v>
       </c>
@@ -7809,7 +7849,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>797</v>
       </c>
@@ -7829,7 +7869,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>800</v>
       </c>
@@ -7849,7 +7889,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>803</v>
       </c>
@@ -7869,7 +7909,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>807</v>
       </c>
@@ -7889,7 +7929,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
         <v>811</v>
       </c>
@@ -7909,7 +7949,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>815</v>
       </c>
@@ -7929,7 +7969,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A243" s="7" t="s">
         <v>819</v>
       </c>
@@ -7949,7 +7989,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>822</v>
       </c>
@@ -7969,7 +8009,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A245" s="7" t="s">
         <v>826</v>
       </c>
@@ -7989,7 +8029,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>830</v>
       </c>
@@ -8009,7 +8049,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A247" s="7" t="s">
         <v>834</v>
       </c>
@@ -8029,7 +8069,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>838</v>
       </c>
@@ -8049,7 +8089,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>842</v>
       </c>
@@ -8069,7 +8109,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>846</v>
       </c>
@@ -8089,7 +8129,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A251" s="7" t="s">
         <v>850</v>
       </c>
@@ -8109,7 +8149,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>854</v>
       </c>
@@ -8129,7 +8169,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A253" s="7" t="s">
         <v>733</v>
       </c>
@@ -8149,7 +8189,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>858</v>
       </c>
@@ -8167,6 +8207,26 @@
       </c>
       <c r="F254" s="2" t="s">
         <v>859</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="B255" t="s">
+        <v>861</v>
+      </c>
+      <c r="C255" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D255" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="E255" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F255" s="14" t="s">
+        <v>863</v>
       </c>
     </row>
   </sheetData>
@@ -8560,6 +8620,7 @@
     <hyperlink ref="D253" r:id="rId387" xr:uid="{3CBA59EA-1478-4E2E-BBA5-FE5C3D9A000E}"/>
     <hyperlink ref="B254" r:id="rId388" xr:uid="{50B44BA9-E761-471A-A419-649F43422B2D}"/>
     <hyperlink ref="D254" r:id="rId389" xr:uid="{1D8ABEE3-77DB-4AC6-A75C-D6E458C25DA0}"/>
+    <hyperlink ref="D255" r:id="rId390" xr:uid="{58F9D4C7-7B1C-4CB4-9F24-CEFA98306AD9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vendor_list.xlsx
+++ b/vendor_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pallavi.pen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A364B01C-2407-4F18-980A-063D97E18459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C8EA55-9697-475B-B0E0-F8E7B4B427FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F29C8DE6-4C93-4303-B28F-F3BD5FAA3955}"/>
   </bookViews>
@@ -2616,9 +2616,6 @@
     <t>Primary banking institution; holds company accounts and processes financial transactions</t>
   </si>
   <si>
-    <t>Gafana Labs</t>
-  </si>
-  <si>
     <t xml:space="preserve"> https://grafana.com</t>
   </si>
   <si>
@@ -2626,6 +2623,9 @@
   </si>
   <si>
     <t>Infra Monitoring tool.</t>
+  </si>
+  <si>
+    <t>Gafana</t>
   </si>
 </sst>
 </file>
@@ -8211,22 +8211,22 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="14" t="s">
+        <v>863</v>
+      </c>
+      <c r="B255" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="B255" t="s">
-        <v>861</v>
       </c>
       <c r="C255" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D255" s="16" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E255" s="13" t="s">
         <v>106</v>
       </c>
       <c r="F255" s="14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
